--- a/EXCEL/Data/løn_data/Løn_stilling_1000kr.xlsx
+++ b/EXCEL/Data/løn_data/Løn_stilling_1000kr.xlsx
@@ -169,7 +169,7 @@
     <t>Datasæt 02 2025</t>
   </si>
   <si>
-    <t>Kørsel 10.4.2026 10.54.21</t>
+    <t>Kørsel 14.4.2026 12.28.05</t>
   </si>
   <si>
     <t/>
